--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129064260</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129064260</v>
+        <v>123524950</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524107</v>
+        <v>524192</v>
       </c>
       <c r="R2" t="n">
-        <v>6714128</v>
+        <v>6713963</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -730,7 +730,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -740,27 +740,27 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Aspeboda</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +784,1068 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123524063</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>524262</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6713854</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123524517</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>524209</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6713935</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123524367</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>524214</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6713917</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123524383</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>524223</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6713905</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126936747</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>524288</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6713820</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126964224</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>524279</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6713844</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126964244</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>524280</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6713844</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129064197</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>524099</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6714137</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129064260</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>524107</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6714128</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5666-2025 artfynd.xlsx
+++ b/artfynd/A 5666-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524063</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524517</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524367</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524383</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936747</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,6 +1522,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126964224</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1613,6 +1653,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126964244</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1734,6 +1779,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064197</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1846,8 +1896,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064260</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>